--- a/htr-FHIR/ig/StructureDefinition-fr-order-extension.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-order-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-order-extension.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-order-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-order-extension.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-order-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-order-extension.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-order-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
